--- a/Result/profitability/6531.xlsx
+++ b/Result/profitability/6531.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM48"/>
+  <dimension ref="A1:AM49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6042,27 +6042,27 @@
         <v>42.25</v>
       </c>
       <c r="G45" t="n">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>20.38%</t>
+          <t>20.27%</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>-955</v>
+        <v>-956</v>
       </c>
       <c r="J45" t="n">
-        <v>-684</v>
+        <v>-686</v>
       </c>
       <c r="K45" t="n">
-        <v>-545</v>
+        <v>-548</v>
       </c>
       <c r="L45" t="n">
-        <v>-3.36</v>
+        <v>-3.37</v>
       </c>
       <c r="M45" t="n">
-        <v>1.74625</v>
+        <v>1.745</v>
       </c>
       <c r="N45" t="n">
         <v>47.07</v>
@@ -6092,10 +6092,10 @@
         <v>114.2</v>
       </c>
       <c r="W45" t="n">
-        <v>-5.4</v>
+        <v>-5.41</v>
       </c>
       <c r="X45" t="n">
-        <v>-2.647058823529412</v>
+        <v>-2.651960784313726</v>
       </c>
       <c r="Y45" t="n">
         <v>-4.229999999999997</v>
@@ -6104,10 +6104,10 @@
         <v>-0.09100688468158347</v>
       </c>
       <c r="AA45" t="n">
-        <v>-5.64</v>
+        <v>-5.65</v>
       </c>
       <c r="AB45" t="n">
-        <v>-2.473684210526316</v>
+        <v>-2.478070175438597</v>
       </c>
       <c r="AC45" t="n">
         <v>-9.109999999999999</v>
@@ -6169,27 +6169,27 @@
         <v>46.01</v>
       </c>
       <c r="G46" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>25.49%</t>
+          <t>25.59%</t>
         </is>
       </c>
       <c r="I46" t="n">
         <v>479</v>
       </c>
       <c r="J46" t="n">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="K46" t="n">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="L46" t="n">
-        <v>4.34</v>
+        <v>4.36</v>
       </c>
       <c r="M46" t="n">
-        <v>1.88</v>
+        <v>1.88125</v>
       </c>
       <c r="N46" t="n">
         <v>47.655</v>
@@ -6219,10 +6219,10 @@
         <v>114.3</v>
       </c>
       <c r="W46" t="n">
-        <v>7.699999999999999</v>
+        <v>7.73</v>
       </c>
       <c r="X46" t="n">
-        <v>-2.291666666666667</v>
+        <v>-2.293768545994065</v>
       </c>
       <c r="Y46" t="n">
         <v>3.759999999999998</v>
@@ -6231,10 +6231,10 @@
         <v>0.08899408284023669</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.086538461538461</v>
+        <v>1.096153846153846</v>
       </c>
       <c r="AC46" t="n">
         <v>-6.050000000000004</v>
@@ -6316,7 +6316,7 @@
         <v>4.71</v>
       </c>
       <c r="M47" t="n">
-        <v>2.1825</v>
+        <v>2.18375</v>
       </c>
       <c r="N47" t="n">
         <v>48.41625</v>
@@ -6346,10 +6346,10 @@
         <v>114.4</v>
       </c>
       <c r="W47" t="n">
-        <v>0.3700000000000001</v>
+        <v>0.3499999999999996</v>
       </c>
       <c r="X47" t="n">
-        <v>0.08525345622119818</v>
+        <v>0.08027522935779818</v>
       </c>
       <c r="Y47" t="n">
         <v>3.850000000000001</v>
@@ -6443,7 +6443,7 @@
         <v>4.15</v>
       </c>
       <c r="M48" t="n">
-        <v>2.4175</v>
+        <v>2.41875</v>
       </c>
       <c r="N48" t="n">
         <v>48.43125</v>
@@ -6524,6 +6524,133 @@
       </c>
       <c r="AM48" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>6531</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2363</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1204</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1159</v>
+      </c>
+      <c r="F49" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="G49" t="n">
+        <v>726</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>30.71%</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>109</v>
+      </c>
+      <c r="J49" t="n">
+        <v>835</v>
+      </c>
+      <c r="K49" t="n">
+        <v>681</v>
+      </c>
+      <c r="L49" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2.65625</v>
+      </c>
+      <c r="N49" t="n">
+        <v>48.14375</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.02999999999999936</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0.007228915662650381</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>2.870000000000005</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.06213466118207411</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>-2.240356083086053</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>6.810000000000002</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.1611834319526628</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK49" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
